--- a/Magnetometer_Operations/Forms/IZZI_sheet.xlsx
+++ b/Magnetometer_Operations/Forms/IZZI_sheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yimingzhang/Github/lab_protocols/Magnetometer_Operations/Forms/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97C546E0-F5D3-AD44-B920-39500BD35CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6479DF6-58AC-044A-9142-9936C209B504}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="9600" yWindow="2400" windowWidth="28040" windowHeight="17440" xr2:uid="{2DFFAAAF-4D58-B840-BC3F-3CD338D56050}"/>
   </bookViews>
@@ -44,9 +44,6 @@
     <t>oven demag</t>
   </si>
   <si>
-    <t>iZZI step</t>
-  </si>
-  <si>
     <t>N</t>
   </si>
   <si>
@@ -72,6 +69,9 @@
   </si>
   <si>
     <t>AF</t>
+  </si>
+  <si>
+    <t>IZZI step</t>
   </si>
 </sst>
 </file>
@@ -164,9 +164,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2013 - 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -204,7 +204,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -310,7 +310,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -452,7 +452,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme 2013 - 2022" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -475,33 +475,33 @@
   <sheetData>
     <row r="1" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B2" s="2">
         <v>0</v>
@@ -515,7 +515,7 @@
     </row>
     <row r="3" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2">
         <v>100</v>
@@ -529,7 +529,7 @@
     </row>
     <row r="4" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" s="2">
         <v>100.1</v>
@@ -543,7 +543,7 @@
     </row>
     <row r="5" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2">
         <v>200.1</v>
@@ -557,7 +557,7 @@
     </row>
     <row r="6" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="2">
         <v>200</v>
@@ -571,7 +571,7 @@
     </row>
     <row r="7" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="2">
         <v>300</v>
@@ -585,7 +585,7 @@
     </row>
     <row r="8" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" s="2">
         <v>100.2</v>
@@ -599,7 +599,7 @@
     </row>
     <row r="9" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="2">
         <v>300.10000000000002</v>
@@ -613,7 +613,7 @@
     </row>
     <row r="10" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B10" s="2">
         <v>400.1</v>
@@ -627,7 +627,7 @@
     </row>
     <row r="11" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" s="2">
         <v>400</v>
@@ -641,7 +641,7 @@
     </row>
     <row r="12" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="2">
         <v>425</v>
@@ -655,7 +655,7 @@
     </row>
     <row r="13" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="2">
         <v>300.2</v>
@@ -669,7 +669,7 @@
     </row>
     <row r="14" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B14" s="2">
         <v>425.1</v>
@@ -683,7 +683,7 @@
     </row>
     <row r="15" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B15" s="2">
         <v>450.1</v>
@@ -697,7 +697,7 @@
     </row>
     <row r="16" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B16" s="2">
         <v>450</v>
@@ -711,7 +711,7 @@
     </row>
     <row r="17" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B17" s="2">
         <v>475</v>
@@ -725,7 +725,7 @@
     </row>
     <row r="18" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" s="2">
         <v>425.2</v>
@@ -739,7 +739,7 @@
     </row>
     <row r="19" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B19" s="2">
         <v>475.1</v>
@@ -753,7 +753,7 @@
     </row>
     <row r="20" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B20" s="2">
         <v>500.1</v>
@@ -767,7 +767,7 @@
     </row>
     <row r="21" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B21" s="2">
         <v>500</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="22" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B22" s="2">
         <v>520</v>
@@ -795,7 +795,7 @@
     </row>
     <row r="23" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B23" s="2">
         <v>475.2</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="24" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B24" s="2">
         <v>520.1</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="25" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B25" s="2">
         <v>530.1</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="26" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B26" s="2">
         <v>530</v>
@@ -851,7 +851,7 @@
     </row>
     <row r="27" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B27" s="2">
         <v>540</v>
@@ -865,7 +865,7 @@
     </row>
     <row r="28" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B28" s="2">
         <v>520.20000000000005</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="29" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B29" s="2">
         <v>540.1</v>
@@ -893,7 +893,7 @@
     </row>
     <row r="30" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B30" s="2">
         <v>550.1</v>
@@ -907,7 +907,7 @@
     </row>
     <row r="31" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B31" s="2">
         <v>550</v>
@@ -921,7 +921,7 @@
     </row>
     <row r="32" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B32" s="2">
         <v>555</v>
@@ -935,7 +935,7 @@
     </row>
     <row r="33" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B33" s="2">
         <v>540.20000000000005</v>
@@ -949,7 +949,7 @@
     </row>
     <row r="34" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B34" s="2">
         <v>555.1</v>
@@ -963,7 +963,7 @@
     </row>
     <row r="35" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B35" s="2">
         <v>560.1</v>
@@ -977,7 +977,7 @@
     </row>
     <row r="36" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B36" s="2">
         <v>560</v>
@@ -991,7 +991,7 @@
     </row>
     <row r="37" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B37" s="2">
         <v>562</v>
@@ -1005,7 +1005,7 @@
     </row>
     <row r="38" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B38" s="2">
         <v>555.20000000000005</v>
@@ -1019,7 +1019,7 @@
     </row>
     <row r="39" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B39" s="2">
         <v>562.1</v>
@@ -1033,7 +1033,7 @@
     </row>
     <row r="40" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B40" s="2">
         <v>564.1</v>
@@ -1047,7 +1047,7 @@
     </row>
     <row r="41" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B41" s="2">
         <v>564</v>
@@ -1061,7 +1061,7 @@
     </row>
     <row r="42" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B42" s="2">
         <v>566</v>
@@ -1075,7 +1075,7 @@
     </row>
     <row r="43" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B43" s="2">
         <v>562.20000000000005</v>
@@ -1089,7 +1089,7 @@
     </row>
     <row r="44" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B44" s="2">
         <v>566.1</v>
@@ -1103,7 +1103,7 @@
     </row>
     <row r="45" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B45" s="2">
         <v>570.1</v>
@@ -1117,7 +1117,7 @@
     </row>
     <row r="46" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B46" s="2">
         <v>570</v>
@@ -1131,7 +1131,7 @@
     </row>
     <row r="47" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B47" s="2">
         <v>575</v>
@@ -1145,7 +1145,7 @@
     </row>
     <row r="48" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B48" s="2">
         <v>566.20000000000005</v>
@@ -1159,7 +1159,7 @@
     </row>
     <row r="49" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B49" s="2">
         <v>575.1</v>
@@ -1173,7 +1173,7 @@
     </row>
     <row r="50" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B50" s="2">
         <v>580.1</v>
@@ -1187,7 +1187,7 @@
     </row>
     <row r="51" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B51" s="2">
         <v>580</v>
@@ -1201,7 +1201,7 @@
     </row>
     <row r="52" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B52" s="2">
         <v>585</v>
@@ -1215,7 +1215,7 @@
     </row>
     <row r="53" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B53" s="2">
         <v>575.20000000000005</v>
@@ -1229,7 +1229,7 @@
     </row>
     <row r="54" spans="1:8" ht="12" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B54" s="2">
         <v>585.1</v>
